--- a/SeleniumBDDFramework/SeleniumBDDFramework/src/test/resources/TestData/CRMActivityData.xlsx
+++ b/SeleniumBDDFramework/SeleniumBDDFramework/src/test/resources/TestData/CRMActivityData.xlsx
@@ -8,7 +8,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="General Activity" sheetId="1" r:id="rId1"/>
@@ -36,138 +36,141 @@
     <t>Description</t>
   </si>
   <si>
+    <t>Date(DD-MM-YYYY)</t>
+  </si>
+  <si>
+    <t>Start Time</t>
+  </si>
+  <si>
+    <t>End Time</t>
+  </si>
+  <si>
+    <t>Assignment Type</t>
+  </si>
+  <si>
+    <t>Users</t>
+  </si>
+  <si>
+    <t>Reason for Assignment </t>
+  </si>
+  <si>
+    <t>Edit Required</t>
+  </si>
+  <si>
+    <t>Edit Purpose</t>
+  </si>
+  <si>
+    <t>Edit Description</t>
+  </si>
+  <si>
+    <t>aarav@onelern.com</t>
+  </si>
+  <si>
+    <t>Call</t>
+  </si>
+  <si>
+    <t>Automation Activity</t>
+  </si>
+  <si>
+    <t>Created through Selenium Automation</t>
+  </si>
+  <si>
+    <t>I am doing this activity myself</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>Automation Activity Updation</t>
+  </si>
+  <si>
+    <t>Created through Selenium Automation Updation</t>
+  </si>
+  <si>
+    <t>bhavya35@onelern.com</t>
+  </si>
+  <si>
+    <t>I want to assign this activity to my teammate</t>
+  </si>
+  <si>
+    <t>John John</t>
+  </si>
+  <si>
+    <t>Automated activity updation</t>
+  </si>
+  <si>
+    <t>keerthi1@onelern.com</t>
+  </si>
+  <si>
+    <t>I want to tag users for collaboration</t>
+  </si>
+  <si>
+    <t>Surya Rana</t>
+  </si>
+  <si>
+    <t>kiara@onelern.com</t>
+  </si>
+  <si>
+    <t>Physical Visit</t>
+  </si>
+  <si>
+    <t>NO</t>
+  </si>
+  <si>
+    <t>lakshmi@onelern.com</t>
+  </si>
+  <si>
+    <t>Vihaan Das</t>
+  </si>
+  <si>
+    <t>Automated activity</t>
+  </si>
+  <si>
+    <t>niharika@onelern.com</t>
+  </si>
+  <si>
+    <t>Keerthi Chowdary</t>
+  </si>
+  <si>
+    <t>priya@onelern.com</t>
+  </si>
+  <si>
+    <t>Virtual Visit</t>
+  </si>
+  <si>
+    <t>kiran@onelern.com</t>
+  </si>
+  <si>
+    <t>Niharika Reddy</t>
+  </si>
+  <si>
+    <t>sai@onelern.com</t>
+  </si>
+  <si>
+    <t>Rishi Kulkarni</t>
+  </si>
+  <si>
+    <t>rahul@onelern.com</t>
+  </si>
+  <si>
+    <t>sneha@onelern.com</t>
+  </si>
+  <si>
+    <t>Rahul Mishra</t>
+  </si>
+  <si>
+    <t>vikram@onelern.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lead Name </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Link to Stage </t>
+  </si>
+  <si>
     <t>Date</t>
   </si>
   <si>
-    <t>Start Time</t>
-  </si>
-  <si>
-    <t>End Time</t>
-  </si>
-  <si>
-    <t>Assignment Type</t>
-  </si>
-  <si>
-    <t>Users</t>
-  </si>
-  <si>
-    <t>Reason for Assignment </t>
-  </si>
-  <si>
-    <t>Edit Required</t>
-  </si>
-  <si>
-    <t>Edit Purpose</t>
-  </si>
-  <si>
-    <t>Edit Description</t>
-  </si>
-  <si>
-    <t>aarav@onelern.com</t>
-  </si>
-  <si>
-    <t>Call</t>
-  </si>
-  <si>
-    <t>Automation Activity</t>
-  </si>
-  <si>
-    <t>Created through Selenium Automation</t>
-  </si>
-  <si>
-    <t>I am doing this activity myself</t>
-  </si>
-  <si>
-    <t>Yes</t>
-  </si>
-  <si>
-    <t>Automation Activity Updation</t>
-  </si>
-  <si>
-    <t>Created through Selenium Automation Updation</t>
-  </si>
-  <si>
-    <t>bhavya35@onelern.com</t>
-  </si>
-  <si>
-    <t>I want to assign this activity to my teammate</t>
-  </si>
-  <si>
-    <t>John John</t>
-  </si>
-  <si>
-    <t>Automated activity updation</t>
-  </si>
-  <si>
-    <t>keerthi1@onelern.com</t>
-  </si>
-  <si>
-    <t>I want to tag users for collaboration</t>
-  </si>
-  <si>
-    <t>Surya Rana</t>
-  </si>
-  <si>
-    <t>kiara@onelern.com</t>
-  </si>
-  <si>
-    <t>Physical Visit</t>
-  </si>
-  <si>
-    <t>NO</t>
-  </si>
-  <si>
-    <t>lakshmi@onelern.com</t>
-  </si>
-  <si>
-    <t>Vihaan Das</t>
-  </si>
-  <si>
-    <t>Automated activity</t>
-  </si>
-  <si>
-    <t>niharika@onelern.com</t>
-  </si>
-  <si>
-    <t>Keerthi Chowdary</t>
-  </si>
-  <si>
-    <t>priya@onelern.com</t>
-  </si>
-  <si>
-    <t>Virtual Visit</t>
-  </si>
-  <si>
-    <t>kiran@onelern.com</t>
-  </si>
-  <si>
-    <t>Niharika Reddy</t>
-  </si>
-  <si>
-    <t>sai@onelern.com</t>
-  </si>
-  <si>
-    <t>rahul@onelern.com</t>
-  </si>
-  <si>
-    <t>sneha@onelern.com</t>
-  </si>
-  <si>
-    <t>Rahul Mishra</t>
-  </si>
-  <si>
-    <t>vikram@onelern.com</t>
-  </si>
-  <si>
-    <t>Rishi Kulkarni</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lead Name </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Link to Stage </t>
-  </si>
-  <si>
     <t>Little ville School</t>
   </si>
   <si>
@@ -183,7 +186,10 @@
     <t>Created Linked Activity through Automation Updation</t>
   </si>
   <si>
-    <t>intromeet</t>
+    <t>Greenwood High School</t>
+  </si>
+  <si>
+    <t>Teams</t>
   </si>
   <si>
     <t>Prospect</t>
@@ -195,13 +201,19 @@
     <t>Automated Linked activity</t>
   </si>
   <si>
-    <t>Customercare</t>
+    <t>Delhi Public School</t>
+  </si>
+  <si>
+    <t>interview</t>
   </si>
   <si>
     <t>Opportunity</t>
   </si>
   <si>
-    <t>ACHYUTH REDDY</t>
+    <t>Aarav Sharma</t>
+  </si>
+  <si>
+    <t>Oakridge International School</t>
   </si>
   <si>
     <t>reports</t>
@@ -210,13 +222,16 @@
     <t>Verbal Commitment</t>
   </si>
   <si>
+    <t>Sri Chaitanya School</t>
+  </si>
+  <si>
     <t>walkin</t>
   </si>
   <si>
     <t>Deal Won</t>
   </si>
   <si>
-    <t>interview</t>
+    <t>Narayana School</t>
   </si>
   <si>
     <t>Closure Stage</t>
@@ -225,13 +240,16 @@
     <t>Mukesh Gautam</t>
   </si>
   <si>
+    <t>St. Mary's High School</t>
+  </si>
+  <si>
     <t>Online</t>
   </si>
   <si>
     <t>Lead Qualification</t>
   </si>
   <si>
-    <t>Teams</t>
+    <t>Little Flower School</t>
   </si>
   <si>
     <t>Product Demo</t>
@@ -240,19 +258,31 @@
     <t>Anjali Verma</t>
   </si>
   <si>
+    <t>Vignan Global School</t>
+  </si>
+  <si>
     <t>Zoom</t>
   </si>
   <si>
     <t>Hot Lead</t>
   </si>
   <si>
+    <t>Sentia The Global School</t>
+  </si>
+  <si>
     <t>Audio</t>
   </si>
   <si>
+    <t>Silver Oaks School</t>
+  </si>
+  <si>
     <t>login</t>
   </si>
   <si>
     <t>Cold Deal</t>
+  </si>
+  <si>
+    <t>Lotus Valley School</t>
   </si>
   <si>
     <t>logout</t>
@@ -722,7 +752,7 @@
     <col min="3" max="3" width="18.19922" customWidth="1"/>
     <col min="4" max="4" width="22.09766" customWidth="1"/>
     <col min="5" max="5" width="43.09766" customWidth="1"/>
-    <col min="6" max="6" width="13.09766" customWidth="1"/>
+    <col min="6" max="6" width="24.29688" customWidth="1"/>
     <col min="7" max="7" width="15.29688" customWidth="1"/>
     <col min="8" max="8" width="16.29688" customWidth="1"/>
     <col min="9" max="9" width="42.09766" customWidth="1"/>
@@ -794,7 +824,7 @@
         <v>17</v>
       </c>
       <c r="F2" s="10">
-        <v>46259</v>
+        <v>46287</v>
       </c>
       <c r="G2" s="11">
         <v>0.375</v>
@@ -834,7 +864,7 @@
         <v>17</v>
       </c>
       <c r="F3" s="10">
-        <v>46259</v>
+        <v>46287</v>
       </c>
       <c r="G3" s="11">
         <v>0.41666666666666652</v>
@@ -878,7 +908,7 @@
         <v>17</v>
       </c>
       <c r="F4" s="10">
-        <v>46259</v>
+        <v>46287</v>
       </c>
       <c r="G4" s="11">
         <v>0.54166666666666652</v>
@@ -920,7 +950,7 @@
         <v>17</v>
       </c>
       <c r="F5" s="10">
-        <v>46260</v>
+        <v>46288</v>
       </c>
       <c r="G5" s="11">
         <v>0.375</v>
@@ -956,7 +986,7 @@
         <v>17</v>
       </c>
       <c r="F6" s="10">
-        <v>46260</v>
+        <v>46288</v>
       </c>
       <c r="G6" s="11">
         <v>0.41666666666666652</v>
@@ -996,7 +1026,7 @@
         <v>17</v>
       </c>
       <c r="F7" s="10">
-        <v>46260</v>
+        <v>46288</v>
       </c>
       <c r="G7" s="11">
         <v>0.54166666666666652</v>
@@ -1034,7 +1064,7 @@
         <v>17</v>
       </c>
       <c r="F8" s="10">
-        <v>46261</v>
+        <v>46289</v>
       </c>
       <c r="G8" s="11">
         <v>0.375</v>
@@ -1070,7 +1100,7 @@
         <v>17</v>
       </c>
       <c r="F9" s="10">
-        <v>46261</v>
+        <v>46289</v>
       </c>
       <c r="G9" s="11">
         <v>0.41666666666666652</v>
@@ -1110,7 +1140,7 @@
         <v>17</v>
       </c>
       <c r="F10" s="10">
-        <v>46261</v>
+        <v>46289</v>
       </c>
       <c r="G10" s="11">
         <v>0.54166666666666652</v>
@@ -1122,7 +1152,7 @@
         <v>27</v>
       </c>
       <c r="J10" s="13" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="K10" s="5"/>
       <c r="L10" s="5" t="s">
@@ -1133,7 +1163,7 @@
     </row>
     <row r="11" ht="17.4">
       <c r="A11" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B11" s="6">
         <v>123456</v>
@@ -1148,7 +1178,7 @@
         <v>17</v>
       </c>
       <c r="F11" s="10">
-        <v>46262</v>
+        <v>46286</v>
       </c>
       <c r="G11" s="11">
         <v>0.375</v>
@@ -1169,7 +1199,7 @@
     </row>
     <row r="12" ht="17.4">
       <c r="A12" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B12" s="6">
         <v>123456</v>
@@ -1184,7 +1214,7 @@
         <v>17</v>
       </c>
       <c r="F12" s="10">
-        <v>46262</v>
+        <v>46286</v>
       </c>
       <c r="G12" s="11">
         <v>0.41666666666666652</v>
@@ -1196,7 +1226,7 @@
         <v>23</v>
       </c>
       <c r="J12" s="13" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K12" s="5" t="s">
         <v>34</v>
@@ -1209,7 +1239,7 @@
     </row>
     <row r="13" ht="17.4">
       <c r="A13" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B13" s="6">
         <v>123456</v>
@@ -1224,7 +1254,7 @@
         <v>17</v>
       </c>
       <c r="F13" s="10">
-        <v>46262</v>
+        <v>46286</v>
       </c>
       <c r="G13" s="11">
         <v>0.54166666666666652</v>
@@ -1236,7 +1266,7 @@
         <v>27</v>
       </c>
       <c r="J13" s="13" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="K13" s="5"/>
       <c r="L13" s="5" t="s">
@@ -1296,7 +1326,7 @@
         <v>48</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>5</v>
+        <v>49</v>
       </c>
       <c r="I1" s="2" t="s">
         <v>6</v>
@@ -1328,22 +1358,22 @@
         <v>123456</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>15</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H2" s="18">
-        <v>46259</v>
+        <v>46290</v>
       </c>
       <c r="I2" s="11">
         <v>0.375</v>
@@ -1360,7 +1390,7 @@
         <v>19</v>
       </c>
       <c r="O2" s="9" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3" ht="17.4">
@@ -1371,22 +1401,22 @@
         <v>123456</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="H3" s="18">
-        <v>46259</v>
+        <v>46290</v>
       </c>
       <c r="I3" s="11">
         <v>0.41666666666666652</v>
@@ -1398,16 +1428,16 @@
         <v>23</v>
       </c>
       <c r="L3" s="5" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="M3" s="5" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="N3" s="5" t="s">
         <v>19</v>
       </c>
       <c r="O3" s="9" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4" ht="17.4">
@@ -1418,22 +1448,22 @@
         <v>123456</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="H4" s="18">
-        <v>46259</v>
+        <v>46290</v>
       </c>
       <c r="I4" s="11">
         <v>0.54166666666666652</v>
@@ -1445,14 +1475,14 @@
         <v>27</v>
       </c>
       <c r="L4" s="5" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M4" s="5"/>
       <c r="N4" s="19" t="s">
         <v>19</v>
       </c>
       <c r="O4" s="9" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5" ht="17.4">
@@ -1463,22 +1493,22 @@
         <v>123456</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="D5" s="7" t="s">
         <v>30</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="H5" s="18">
-        <v>46260</v>
+        <v>46291</v>
       </c>
       <c r="I5" s="11">
         <v>0.375</v>
@@ -1504,22 +1534,22 @@
         <v>123456</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>30</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="H6" s="18">
-        <v>46260</v>
+        <v>46291</v>
       </c>
       <c r="I6" s="11">
         <v>0.41666666666666652</v>
@@ -1547,22 +1577,22 @@
         <v>123456</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>49</v>
+        <v>70</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>30</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="H7" s="18">
-        <v>46260</v>
+        <v>46291</v>
       </c>
       <c r="I7" s="11">
         <v>0.54166666666666652</v>
@@ -1574,10 +1604,10 @@
         <v>23</v>
       </c>
       <c r="L7" s="5" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="M7" s="5" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="N7" s="5" t="s">
         <v>31</v>
@@ -1592,22 +1622,22 @@
         <v>123456</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>49</v>
+        <v>73</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>38</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="H8" s="18">
-        <v>46261</v>
+        <v>46292</v>
       </c>
       <c r="I8" s="11">
         <v>0.375</v>
@@ -1633,22 +1663,22 @@
         <v>123456</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>38</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="H9" s="18">
-        <v>46261</v>
+        <v>46292</v>
       </c>
       <c r="I9" s="11">
         <v>0.41666666666666652</v>
@@ -1660,7 +1690,7 @@
         <v>27</v>
       </c>
       <c r="L9" s="5" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="M9" s="5"/>
       <c r="N9" s="5" t="s">
@@ -1676,22 +1706,22 @@
         <v>123456</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>49</v>
+        <v>79</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>38</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="H10" s="18">
-        <v>46261</v>
+        <v>46292</v>
       </c>
       <c r="I10" s="11">
         <v>0.54166666666666652</v>
@@ -1706,7 +1736,7 @@
         <v>40</v>
       </c>
       <c r="M10" s="5" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="N10" s="5" t="s">
         <v>31</v>
@@ -1715,28 +1745,28 @@
     </row>
     <row r="11" ht="17.4">
       <c r="A11" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B11" s="6">
         <v>123456</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>0</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="H11" s="18">
-        <v>46262</v>
+        <v>46293</v>
       </c>
       <c r="I11" s="11">
         <v>0.375</v>
@@ -1748,7 +1778,7 @@
         <v>27</v>
       </c>
       <c r="L11" s="13" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="M11" s="5"/>
       <c r="N11" s="5" t="s">
@@ -1758,28 +1788,28 @@
     </row>
     <row r="12" ht="17.4">
       <c r="A12" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B12" s="6">
         <v>123456</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>49</v>
+        <v>84</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>0</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="H12" s="18">
-        <v>46262</v>
+        <v>46293</v>
       </c>
       <c r="I12" s="11">
         <v>0.41666666666666652</v>
@@ -1799,28 +1829,28 @@
     </row>
     <row r="13" ht="17.4">
       <c r="A13" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B13" s="6">
         <v>123456</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>49</v>
+        <v>87</v>
       </c>
       <c r="D13" s="7" t="s">
         <v>0</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H13" s="18">
-        <v>46262</v>
+        <v>46293</v>
       </c>
       <c r="I13" s="11">
         <v>0.54166666666666652</v>
@@ -1832,10 +1862,10 @@
         <v>23</v>
       </c>
       <c r="L13" s="5" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="M13" s="5" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="N13" s="5" t="s">
         <v>31</v>

--- a/SeleniumBDDFramework/SeleniumBDDFramework/src/test/resources/TestData/CRMActivityData.xlsx
+++ b/SeleniumBDDFramework/SeleniumBDDFramework/src/test/resources/TestData/CRMActivityData.xlsx
@@ -13,6 +13,7 @@
   <sheets>
     <sheet name="General Activity" sheetId="1" r:id="rId1"/>
     <sheet name="Linked Activity" sheetId="2" r:id="rId2"/>
+    <sheet name="Leads" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr/>
 </workbook>
@@ -201,7 +202,7 @@
     <t>Automated Linked activity</t>
   </si>
   <si>
-    <t>Delhi Public School</t>
+    <t>Sahithi Vidhyalayam High school</t>
   </si>
   <si>
     <t>interview</t>
@@ -210,7 +211,7 @@
     <t>Opportunity</t>
   </si>
   <si>
-    <t>Aarav Sharma</t>
+    <t>Divya sharma</t>
   </si>
   <si>
     <t>Oakridge International School</t>
@@ -1288,7 +1289,7 @@
   <cols>
     <col min="1" max="1" width="26.59766" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="3" width="16.29688" customWidth="1"/>
+    <col min="3" max="3" width="26.89844" customWidth="1"/>
     <col min="4" max="4" width="18.09766" customWidth="1"/>
     <col min="5" max="5" width="12.79688" customWidth="1"/>
     <col min="6" max="6" width="48" customWidth="1"/>
@@ -1874,4 +1875,11 @@
     </row>
   </sheetData>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetData/>
+</worksheet>
 </file>